--- a/base_datas/crescimento_medio_receita_uf.xlsx
+++ b/base_datas/crescimento_medio_receita_uf.xlsx
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>456.4609447365203</v>
+        <v>463.1334485384592</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>343.1146435057699</v>
+        <v>344.1634453424787</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>295.0623179330288</v>
+        <v>295.9235665225501</v>
       </c>
     </row>
     <row r="13">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>284.2719903905407</v>
+        <v>284.0865840550747</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>383.8055136001887</v>
+        <v>391.1075878101565</v>
       </c>
     </row>
     <row r="23">
